--- a/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/08062026.xlsx
+++ b/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/08062026.xlsx
@@ -1,117 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Evangelio y Oraciones" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evangelio y Oraciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
-  <si>
-    <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>APELLIDO_PATERNO</t>
-  </si>
-  <si>
-    <t>APELLIDO_MATERNO</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>MAIL</t>
-  </si>
-  <si>
-    <t>CORREO</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>WHATSAPP</t>
-  </si>
-  <si>
-    <t>TEXTO_MENSAJE</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>56994148421</t>
-  </si>
-  <si>
-    <t>lucesalejandro3@gmail.com</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lunes, 8 de junio de 2026
-*Evangelio del Día*
-Lectura del santo evangelio según san Mateo
-Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
-*Oración de la mañana*
-Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
-Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
-Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
-En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>56973223070</t>
-  </si>
-  <si>
-    <t>Mama</t>
-  </si>
-  <si>
-    <t>56971748545</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>56931123918</t>
-  </si>
-  <si>
-    <t>Yume</t>
-  </si>
-  <si>
-    <t>584146711206</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,28 +51,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,193 +456,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="100" style="1" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="8"/>
+    <col width="100" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_PATERNO</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_MATERNO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MAIL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO_MENSAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>56994148421</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>lunes, 8 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
+*Oración de la mañana*
+Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
+Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
+Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
+En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>56973223070</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>lunes, 8 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
+*Oración de la mañana*
+Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
+Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
+Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
+En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56971748545</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>lunes, 8 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
+*Oración de la mañana*
+Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
+Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
+Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
+En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56931123918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>lunes, 8 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
+*Oración de la mañana*
+Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
+Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
+Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
+En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>584146711206</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>lunes, 8 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
+*Oración de la mañana*
+Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
+Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
+Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
+En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mariangely</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>56972028078</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mariangelygonzalez14@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>lunes, 8 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
+*Oración de la mañana*
+Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
+Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
+Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
+En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUCES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34672527995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>alejandroluces5515@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>lunes, 8 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
+*Oración de la mañana*
+Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
+Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
+Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
+En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marianny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>56967970252</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>marikaro2508@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>lunes, 8 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
+*Oración de la mañana*
+Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
+Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
+Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
+En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Milagros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>56936637515</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Milagrosghurtado@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>lunes, 8 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 5, 1-12 En aquel tiempo, cuando Jesús vio a la muchedumbre, subió al monte y se sentó. Entonces se le acercaron sus discípulos. Enseguida comenzó a enseñarles, hablándoles así: "Dichosos los pobres de espíritu, porque de ellos es el Reino de los cielos. Dichosos los que lloran, porque serán consolados. Dichosos los sufridos, porque heredarán la tierra. Dichosos los que tienen hambre y sed de justicia, porque serán saciados. Dichosos los misericordiosos, porque obtendrán misericordia. Dichosos los limpios de corazón, porque verán a Dios. Dichosos los que trabajan por la paz, porque se les llamará hijos de Dios. Dichosos los perseguidos por causa de la justicia, porque de ellos es el Reino de los cielos. Dichosos serán ustedes cuando los injurien, los persigan y digan cosas falsas de ustedes por causa mía. Alégrense y salten de contento, porque su premio será grande en los cielos, puesto que de la misma manera persiguieron a los profetas que vivieron antes que ustedes".
+*Oración de la mañana*
+Querido Jesús, maestro de las bienaventuranzas, enséñanos a ser pobres de espíritu, humildes y conscientes de nuestras necesidades y limitaciones. Ayúdanos a consolar a los que lloran, a ser portadores de paz y trabajadores de justicia.
+Padre eterno, gracias por este nuevo día que nos regalas. Ayúdanos a tener hambre y sed de justicia, a ser misericordiosos y limpios de corazón. Con tu amor paternal, danos la fuerza para enfrentar las persecuciones y las injurias, sabiendo que el Reino de los cielos nos espera.
+Espíritu Santo, llena nuestros corazones de tu amor y guía nuestros pasos en el camino de la paz. Inspíranos para ser sal y luz en este mundo, para trabajar por la paz y para ser misericordiosos. Ayúdanos a alegrarnos y saltar de contento en medio de las tribulaciones, confiando en que nuestro premio será grande en los cielos.
+En la unidad y amor de la Trinidad, comenzamos este día con gratitud y esperanza. Amén.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>